--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_reinsurance.xlsx
@@ -588,37 +588,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.02895</v>
+        <v>-0.2508</v>
       </c>
       <c r="E2">
-        <v>0.0638</v>
+        <v>-0.187</v>
       </c>
       <c r="G2">
-        <v>0.03515971935617004</v>
+        <v>0.09460638220542271</v>
       </c>
       <c r="H2">
-        <v>0.03515971935617004</v>
+        <v>0.09460638220542271</v>
       </c>
       <c r="I2">
-        <v>0.1051577515609968</v>
+        <v>0.07128990847801768</v>
       </c>
       <c r="J2">
-        <v>0.1001290539542979</v>
+        <v>0.07128990847801768</v>
       </c>
       <c r="K2">
-        <v>42.48</v>
+        <v>13.996</v>
       </c>
       <c r="L2">
-        <v>0.07012794056954189</v>
+        <v>0.02543432434397034</v>
       </c>
       <c r="M2">
-        <v>15.1</v>
+        <v>0.035</v>
       </c>
       <c r="N2">
-        <v>0.0507563025210084</v>
+        <v>0.0001203824723120314</v>
       </c>
       <c r="O2">
-        <v>0.3554613935969868</v>
+        <v>0.002500714489854244</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,79 +630,79 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>15.1</v>
+        <v>0.035</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>40.15</v>
+        <v>34.48</v>
       </c>
       <c r="V2">
-        <v>0.1349579831932773</v>
+        <v>0.1185939327233955</v>
       </c>
       <c r="W2">
-        <v>0.4992527404496584</v>
+        <v>-0.0133965939243372</v>
       </c>
       <c r="X2">
-        <v>0.09393394476885086</v>
+        <v>0.129534801660534</v>
       </c>
       <c r="Y2">
-        <v>0.4053187956808075</v>
+        <v>-0.1429313955848712</v>
       </c>
       <c r="Z2">
-        <v>1.168624431805785</v>
+        <v>1.048633862061847</v>
       </c>
       <c r="AA2">
-        <v>0.8070707038142573</v>
+        <v>0.008925238404088438</v>
       </c>
       <c r="AB2">
-        <v>0.08329540110138509</v>
+        <v>0.1174521337219417</v>
       </c>
       <c r="AC2">
-        <v>0.7237753027128722</v>
+        <v>-0.1085268953178533</v>
       </c>
       <c r="AD2">
-        <v>96.71599999999999</v>
+        <v>93.616</v>
       </c>
       <c r="AE2">
-        <v>0.7884599596308488</v>
+        <v>2.592945813582189</v>
       </c>
       <c r="AF2">
-        <v>97.50445995963084</v>
+        <v>96.20894581358219</v>
       </c>
       <c r="AG2">
-        <v>57.35445995963084</v>
+        <v>61.72894581358219</v>
       </c>
       <c r="AH2">
-        <v>0.2468439469508666</v>
+        <v>0.2486347277967056</v>
       </c>
       <c r="AI2">
-        <v>0.1731551903648942</v>
+        <v>0.1665929965431879</v>
       </c>
       <c r="AJ2">
-        <v>0.1616281220367235</v>
+        <v>0.1751330054654804</v>
       </c>
       <c r="AK2">
-        <v>0.1096739092043661</v>
+        <v>0.1136752401312568</v>
       </c>
       <c r="AL2">
-        <v>9.869999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="AM2">
-        <v>9.869999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="AN2">
-        <v>1.514334476333631</v>
+        <v>2.355001006238679</v>
       </c>
       <c r="AO2">
-        <v>6.401215805471125</v>
+        <v>1.5259375</v>
       </c>
       <c r="AP2">
-        <v>0.8980296547454998</v>
+        <v>1.552851323545537</v>
       </c>
       <c r="AQ2">
-        <v>6.401215805471125</v>
+        <v>1.5259375</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oxbridge Re Holdings Limited (NasdaqCM:OXBR)</t>
+          <t>Greenlight Capital Re, Ltd. (NasdaqGS:GLRE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,37 +722,37 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0133</v>
+        <v>-0.0576</v>
       </c>
       <c r="E3">
-        <v>0.0638</v>
+        <v>-0.187</v>
       </c>
       <c r="G3">
-        <v>0.01132947976878613</v>
+        <v>0.07913931436907366</v>
       </c>
       <c r="H3">
-        <v>0.01132947976878613</v>
+        <v>0.07913931436907366</v>
       </c>
       <c r="I3">
-        <v>0.8475478925890449</v>
+        <v>0.07292922687551374</v>
       </c>
       <c r="J3">
-        <v>0.8475478925890449</v>
+        <v>0.07292922687551374</v>
       </c>
       <c r="K3">
-        <v>7.18</v>
+        <v>14.9</v>
       </c>
       <c r="L3">
-        <v>0.830057803468208</v>
+        <v>0.02716994894237783</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.035</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0001233262861169838</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.002348993288590604</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -764,70 +764,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.035</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>32.3</v>
       </c>
       <c r="V3">
-        <v>0.08540372670807453</v>
+        <v>0.1138125440451022</v>
       </c>
       <c r="W3">
-        <v>0.9158163265306122</v>
+        <v>0.03307436182019978</v>
       </c>
       <c r="X3">
-        <v>0.08226490096400761</v>
+        <v>0.1404773055048874</v>
       </c>
       <c r="Y3">
-        <v>0.8335514255666046</v>
+        <v>-0.1074029436846876</v>
       </c>
       <c r="Z3">
-        <v>1.787354916088293</v>
+        <v>1.070961846182058</v>
       </c>
       <c r="AA3">
-        <v>1.514868892439302</v>
+        <v>0.07810441945523036</v>
       </c>
       <c r="AB3">
-        <v>0.08164392555838974</v>
+        <v>0.1188023360459336</v>
       </c>
       <c r="AC3">
-        <v>1.433224966880912</v>
+        <v>-0.04069791659070325</v>
       </c>
       <c r="AD3">
-        <v>0.216</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AE3">
-        <v>0.2235536455238081</v>
+        <v>2.463059907341333</v>
       </c>
       <c r="AF3">
-        <v>0.4395536455238082</v>
+        <v>95.86305990734134</v>
       </c>
       <c r="AG3">
-        <v>-2.310446354476192</v>
+        <v>63.56305990734134</v>
       </c>
       <c r="AH3">
-        <v>0.01346690124189515</v>
+        <v>0.2524950937569149</v>
       </c>
       <c r="AI3">
-        <v>0.02828611783520708</v>
+        <v>0.1703132906308016</v>
       </c>
       <c r="AJ3">
-        <v>-0.0772994599342971</v>
+        <v>0.1829873905541271</v>
       </c>
       <c r="AK3">
-        <v>-0.1806510546429289</v>
+        <v>0.1198030257109157</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="AN3">
-        <v>0.02924451665312754</v>
+        <v>2.306913330204757</v>
+      </c>
+      <c r="AO3">
+        <v>1.55859375</v>
       </c>
       <c r="AP3">
-        <v>-0.312814291155726</v>
+        <v>1.569962207803526</v>
+      </c>
+      <c r="AQ3">
+        <v>1.55859375</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re, Ltd. (NasdaqGS:GLRE)</t>
+          <t>Oxbridge Re Holdings Limited (NasdaqCM:OXBR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,34 +856,34 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0446</v>
+        <v>-0.444</v>
       </c>
       <c r="G4">
-        <v>0.0355049405459722</v>
+        <v>4.606382978723405</v>
       </c>
       <c r="H4">
-        <v>0.0355049405459722</v>
+        <v>4.606382978723405</v>
       </c>
       <c r="I4">
-        <v>0.0944029789602723</v>
+        <v>-0.4069027559830698</v>
       </c>
       <c r="J4">
-        <v>0.0853741812289437</v>
+        <v>-0.4069027559830698</v>
       </c>
       <c r="K4">
-        <v>35.3</v>
+        <v>-0.904</v>
       </c>
       <c r="L4">
-        <v>0.05911907553173672</v>
+        <v>-0.4808510638297873</v>
       </c>
       <c r="M4">
-        <v>15.1</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.05691669807764795</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4277620396600567</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,82 +892,73 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>15.1</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>37.4</v>
+        <v>2.18</v>
       </c>
       <c r="V4">
-        <v>0.1409724839803995</v>
+        <v>0.314121037463977</v>
       </c>
       <c r="W4">
-        <v>0.08268915436870461</v>
+        <v>-0.05986754966887418</v>
       </c>
       <c r="X4">
-        <v>0.1056029885736941</v>
+        <v>0.1185922978161806</v>
       </c>
       <c r="Y4">
-        <v>-0.02291383420498949</v>
+        <v>-0.1784598474850548</v>
       </c>
       <c r="Z4">
-        <v>1.162793174238453</v>
+        <v>0.148079465575211</v>
       </c>
       <c r="AA4">
-        <v>0.0992725151892124</v>
+        <v>-0.06025394264705349</v>
       </c>
       <c r="AB4">
-        <v>0.08494687664438043</v>
+        <v>0.1161019313979497</v>
       </c>
       <c r="AC4">
-        <v>0.01432563854483197</v>
+        <v>-0.1763558740450032</v>
       </c>
       <c r="AD4">
-        <v>96.5</v>
+        <v>0.216</v>
       </c>
       <c r="AE4">
-        <v>0.5649063141070406</v>
+        <v>0.1298859062408557</v>
       </c>
       <c r="AF4">
-        <v>97.06490631410703</v>
+        <v>0.3458859062408557</v>
       </c>
       <c r="AG4">
-        <v>59.66490631410704</v>
+        <v>-1.834114093759144</v>
       </c>
       <c r="AH4">
-        <v>0.2678650846778433</v>
+        <v>0.04747341787833665</v>
       </c>
       <c r="AI4">
-        <v>0.1772664851140522</v>
+        <v>0.02361659161181011</v>
       </c>
       <c r="AJ4">
-        <v>0.1836041528017665</v>
+        <v>-0.3592156439526648</v>
       </c>
       <c r="AK4">
-        <v>0.1169521963891643</v>
+        <v>-0.1471306658470958</v>
       </c>
       <c r="AL4">
-        <v>9.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>9.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>1.708539154760008</v>
-      </c>
-      <c r="AO4">
-        <v>5.663627152988855</v>
+        <v>-0.2938775510204082</v>
       </c>
       <c r="AP4">
-        <v>1.056371280857404</v>
-      </c>
-      <c r="AQ4">
-        <v>5.663627152988855</v>
+        <v>2.495393324842373</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_reinsurance.xlsx
@@ -588,37 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.2508</v>
-      </c>
-      <c r="E2">
-        <v>-0.187</v>
+        <v>0.193</v>
       </c>
       <c r="G2">
-        <v>0.09460638220542271</v>
+        <v>0.06238958623895863</v>
       </c>
       <c r="H2">
-        <v>0.09460638220542271</v>
+        <v>0.06238958623895863</v>
       </c>
       <c r="I2">
-        <v>0.07128990847801768</v>
+        <v>0.1410169840909705</v>
       </c>
       <c r="J2">
-        <v>0.07128990847801768</v>
+        <v>0.1409370609203522</v>
       </c>
       <c r="K2">
-        <v>13.996</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="L2">
-        <v>0.02543432434397034</v>
+        <v>0.1509840384317372</v>
       </c>
       <c r="M2">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0001203824723120314</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.002500714489854244</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,79 +627,76 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.035</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>34.48</v>
+        <v>43.09999999999999</v>
       </c>
       <c r="V2">
-        <v>0.1185939327233955</v>
+        <v>0.1051065697702775</v>
       </c>
       <c r="W2">
-        <v>-0.0133965939243372</v>
+        <v>-0.1183712433177101</v>
       </c>
       <c r="X2">
-        <v>0.129534801660534</v>
+        <v>0.1037386077892338</v>
       </c>
       <c r="Y2">
-        <v>-0.1429313955848712</v>
+        <v>-0.2221098511069439</v>
       </c>
       <c r="Z2">
-        <v>1.048633862061847</v>
+        <v>1.189526633676706</v>
       </c>
       <c r="AA2">
-        <v>0.008925238404088438</v>
+        <v>-0.1596010875171454</v>
       </c>
       <c r="AB2">
-        <v>0.1174521337219417</v>
+        <v>0.09870687509680429</v>
       </c>
       <c r="AC2">
-        <v>-0.1085268953178533</v>
+        <v>-0.2583079626139497</v>
       </c>
       <c r="AD2">
-        <v>93.616</v>
+        <v>75.018</v>
       </c>
       <c r="AE2">
-        <v>2.592945813582189</v>
+        <v>2.04870083048361</v>
       </c>
       <c r="AF2">
-        <v>96.20894581358219</v>
+        <v>77.06670083048361</v>
       </c>
       <c r="AG2">
-        <v>61.72894581358219</v>
+        <v>33.96670083048362</v>
       </c>
       <c r="AH2">
-        <v>0.2486347277967056</v>
+        <v>0.1582066856509724</v>
       </c>
       <c r="AI2">
-        <v>0.1665929965431879</v>
+        <v>0.1166057700367451</v>
       </c>
       <c r="AJ2">
-        <v>0.1751330054654804</v>
+        <v>0.07649697814783239</v>
       </c>
       <c r="AK2">
-        <v>0.1136752401312568</v>
+        <v>0.05497860576579555</v>
       </c>
       <c r="AL2">
-        <v>25.6</v>
+        <v>11.2</v>
       </c>
       <c r="AM2">
-        <v>25.6</v>
+        <v>11.2</v>
       </c>
       <c r="AN2">
-        <v>2.355001006238679</v>
+        <v>-13.41523605150215</v>
       </c>
       <c r="AO2">
-        <v>1.5259375</v>
+        <v>8.102678571428571</v>
       </c>
       <c r="AP2">
-        <v>1.552851323545537</v>
+        <v>-6.074159662103652</v>
       </c>
       <c r="AQ2">
-        <v>1.5259375</v>
+        <v>8.102678571428571</v>
       </c>
     </row>
     <row r="3">
@@ -722,37 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0576</v>
-      </c>
-      <c r="E3">
-        <v>-0.187</v>
+        <v>0.193</v>
       </c>
       <c r="G3">
-        <v>0.07913931436907366</v>
+        <v>0.06508600650860065</v>
       </c>
       <c r="H3">
-        <v>0.07913931436907366</v>
+        <v>0.06508600650860065</v>
       </c>
       <c r="I3">
-        <v>0.07292922687551374</v>
+        <v>0.1506533108202886</v>
       </c>
       <c r="J3">
-        <v>0.07292922687551374</v>
+        <v>0.1504825414573991</v>
       </c>
       <c r="K3">
-        <v>14.9</v>
+        <v>104</v>
       </c>
       <c r="L3">
-        <v>0.02716994894237783</v>
+        <v>0.1611653494498683</v>
       </c>
       <c r="M3">
-        <v>0.035</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0001233262861169838</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.002348993288590604</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -764,79 +755,76 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.035</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>32.3</v>
+        <v>41.3</v>
       </c>
       <c r="V3">
-        <v>0.1138125440451022</v>
+        <v>0.1023290386521308</v>
       </c>
       <c r="W3">
-        <v>0.03307436182019978</v>
+        <v>0.2226980728051392</v>
       </c>
       <c r="X3">
-        <v>0.1404773055048874</v>
+        <v>0.1086002417427042</v>
       </c>
       <c r="Y3">
-        <v>-0.1074029436846876</v>
+        <v>0.114097831062435</v>
       </c>
       <c r="Z3">
-        <v>1.070961846182058</v>
+        <v>1.217301200005355</v>
       </c>
       <c r="AA3">
-        <v>0.07810441945523036</v>
+        <v>0.1831825782959475</v>
       </c>
       <c r="AB3">
-        <v>0.1188023360459336</v>
+        <v>0.09947284690223243</v>
       </c>
       <c r="AC3">
-        <v>-0.04069791659070325</v>
+        <v>0.0837097313937151</v>
       </c>
       <c r="AD3">
-        <v>93.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AE3">
-        <v>2.463059907341333</v>
+        <v>2.007092638338948</v>
       </c>
       <c r="AF3">
-        <v>95.86305990734134</v>
+        <v>76.90709263833895</v>
       </c>
       <c r="AG3">
-        <v>63.56305990734134</v>
+        <v>35.60709263833895</v>
       </c>
       <c r="AH3">
-        <v>0.2524950937569149</v>
+        <v>0.1600540217128996</v>
       </c>
       <c r="AI3">
-        <v>0.1703132906308016</v>
+        <v>0.1178098300487464</v>
       </c>
       <c r="AJ3">
-        <v>0.1829873905541271</v>
+        <v>0.08107130607669692</v>
       </c>
       <c r="AK3">
-        <v>0.1198030257109157</v>
+        <v>0.05822842133312411</v>
       </c>
       <c r="AL3">
-        <v>25.6</v>
+        <v>11.2</v>
       </c>
       <c r="AM3">
-        <v>25.6</v>
+        <v>11.2</v>
       </c>
       <c r="AN3">
-        <v>2.306913330204757</v>
+        <v>121.1974110032363</v>
       </c>
       <c r="AO3">
-        <v>1.55859375</v>
+        <v>8.660714285714286</v>
       </c>
       <c r="AP3">
-        <v>1.569962207803526</v>
+        <v>57.61665475459378</v>
       </c>
       <c r="AQ3">
-        <v>1.55859375</v>
+        <v>8.660714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -855,26 +843,8 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.444</v>
-      </c>
-      <c r="G4">
-        <v>4.606382978723405</v>
-      </c>
-      <c r="H4">
-        <v>4.606382978723405</v>
-      </c>
-      <c r="I4">
-        <v>-0.4069027559830698</v>
-      </c>
-      <c r="J4">
-        <v>-0.4069027559830698</v>
-      </c>
       <c r="K4">
-        <v>-0.904</v>
-      </c>
-      <c r="L4">
-        <v>-0.4808510638297873</v>
+        <v>-6.57</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -898,55 +868,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
-        <v>0.314121037463977</v>
+        <v>0.2786377708978328</v>
       </c>
       <c r="W4">
-        <v>-0.05986754966887418</v>
+        <v>-0.4594405594405594</v>
       </c>
       <c r="X4">
-        <v>0.1185922978161806</v>
+        <v>0.0988769738357634</v>
       </c>
       <c r="Y4">
-        <v>-0.1784598474850548</v>
+        <v>-0.5583175332763228</v>
       </c>
       <c r="Z4">
-        <v>0.148079465575211</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.06025394264705349</v>
+        <v>-0.5023847533302382</v>
       </c>
       <c r="AB4">
-        <v>0.1161019313979497</v>
+        <v>0.09794090329137616</v>
       </c>
       <c r="AC4">
-        <v>-0.1763558740450032</v>
+        <v>-0.6003256566216144</v>
       </c>
       <c r="AD4">
-        <v>0.216</v>
+        <v>0.118</v>
       </c>
       <c r="AE4">
-        <v>0.1298859062408557</v>
+        <v>0.04160819214466147</v>
       </c>
       <c r="AF4">
-        <v>0.3458859062408557</v>
+        <v>0.1596081921446615</v>
       </c>
       <c r="AG4">
-        <v>-1.834114093759144</v>
+        <v>-1.640391807855339</v>
       </c>
       <c r="AH4">
-        <v>0.04747341787833665</v>
+        <v>0.02411142585962487</v>
       </c>
       <c r="AI4">
-        <v>0.02361659161181011</v>
+        <v>0.0196813691072357</v>
       </c>
       <c r="AJ4">
-        <v>-0.3592156439526648</v>
+        <v>-0.3403579175852853</v>
       </c>
       <c r="AK4">
-        <v>-0.1471306658470958</v>
+        <v>-0.2599831491751887</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -955,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-0.2938775510204082</v>
+        <v>-0.01900161030595813</v>
       </c>
       <c r="AP4">
-        <v>2.495393324842373</v>
+        <v>0.2641532701860448</v>
       </c>
     </row>
   </sheetData>
